--- a/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:10:23+00:00</t>
+    <t>2026-06-18T14:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:01:22+00:00</t>
+    <t>2026-06-22T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:03:44+00:00</t>
+    <t>2026-06-22T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:16:05+00:00</t>
+    <t>2026-06-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-lm-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:23:37+00:00</t>
+    <t>2026-06-22T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
